--- a/DADOS_CONTRATOS.xlsx
+++ b/DADOS_CONTRATOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{985BD89F-19F0-41FB-B554-7DEFCD13FFF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0BF4E08-AF90-4D4A-B1EF-751755A209B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -771,12 +771,6 @@
     <t>014/2025</t>
   </si>
   <si>
-    <t>R. SANTANA DE ALMEIDA</t>
-  </si>
-  <si>
-    <t>SERVIÇOS DE REATERRO DE EROSÃO NA ADUTORA DA CAIXA D’ÁGUA DO BAIRRO GLOBO RECREIO, COM EXECUÇÃO DE CIMENTO PARCIAL NO SOLO, MÃO DE OBRA E FORNECIMENTO DOS MATERIAIS</t>
-  </si>
-  <si>
     <t>CE 008/2025</t>
   </si>
   <si>
@@ -793,6 +787,12 @@
   </si>
   <si>
     <t>PE 023/2025</t>
+  </si>
+  <si>
+    <t>SERVIÇOS DE REATERRO DE EROSÃO NA ADUTORA DA CAIXA DÁGUA DO BAIRRO GLOBO RECREIO, COM EXECUÇÃO DE CIMENTO PARCIAL NO SOLO, MÃO DE OBRA E FORNECIMENTO DOS MATERIAIS</t>
+  </si>
+  <si>
+    <t>R SANTANA DE ALMEIDA</t>
   </si>
 </sst>
 </file>
@@ -1328,7 +1328,7 @@
         <v>14</v>
       </c>
       <c r="P1" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2" spans="1:16" s="4" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1376,7 +1376,7 @@
         <v>21</v>
       </c>
       <c r="P2" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:16" ht="240.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1568,7 +1568,7 @@
         <v>45189</v>
       </c>
       <c r="P6" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -1838,7 +1838,7 @@
         <v>45289</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -1976,7 +1976,7 @@
         <v>44886</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.25">
@@ -2066,7 +2066,7 @@
         <v>45077</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.25">
@@ -2111,7 +2111,7 @@
         <v>45077</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2156,7 +2156,7 @@
         <v>45350</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2204,7 +2204,7 @@
         <v>45544</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" spans="1:16" s="4" customFormat="1" ht="144.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2382,7 +2382,7 @@
         <v>45378</v>
       </c>
       <c r="P24" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2427,7 +2427,7 @@
         <v>45519</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.25">
@@ -2475,7 +2475,7 @@
         <v>45568</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="27" spans="1:16" s="21" customFormat="1" x14ac:dyDescent="0.25">
@@ -2604,7 +2604,7 @@
         <v>45688</v>
       </c>
       <c r="P29" s="4" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="30" spans="1:16" ht="105" customHeight="1" x14ac:dyDescent="0.25">
@@ -2853,7 +2853,7 @@
         <v>45560</v>
       </c>
       <c r="P35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="36" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -2898,7 +2898,7 @@
         <v>44823</v>
       </c>
       <c r="P36" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="37" spans="1:16" ht="105" customHeight="1" x14ac:dyDescent="0.25">
@@ -2943,7 +2943,7 @@
         <v>45657</v>
       </c>
       <c r="P37" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="38" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -2988,7 +2988,7 @@
         <v>43517</v>
       </c>
       <c r="P38" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="105" customHeight="1" x14ac:dyDescent="0.25">
@@ -3036,7 +3036,7 @@
         <v>45555</v>
       </c>
       <c r="P39" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -3129,7 +3129,7 @@
         <v>45614</v>
       </c>
       <c r="P41" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -3476,10 +3476,10 @@
         <v>246</v>
       </c>
       <c r="C50" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E50" s="1">
         <v>45932</v>
@@ -3495,7 +3495,7 @@
         <v>131040.5</v>
       </c>
       <c r="I50" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="J50" t="s">
         <v>19</v>
@@ -3512,7 +3512,7 @@
     </row>
     <row r="51" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C51" t="s">
         <v>130</v>
@@ -3534,7 +3534,7 @@
         <v>75617.100000000006</v>
       </c>
       <c r="I51" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="J51" t="s">
         <v>19</v>
@@ -3851,7 +3851,7 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1">
         <f ca="1">TODAY()</f>
-        <v>46021</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="D26" s="1">
         <f ca="1">TODAY()</f>
-        <v>46021</v>
+        <v>46084</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">

--- a/DADOS_CONTRATOS.xlsx
+++ b/DADOS_CONTRATOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0BF4E08-AF90-4D4A-B1EF-751755A209B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48AA8F86-8B66-4058-AE07-1D682D863AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="260">
   <si>
     <t>id</t>
   </si>
@@ -793,6 +793,21 @@
   </si>
   <si>
     <t>R SANTANA DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>OPERAÇÃO, MANUTENÇÃO E CONSERVAÇÃO DO SISTEMA PÚBLICO DE ABASTECIMENTO DE ÁGUA DO MUNICÍPIO DE RONDONÓPOLIS – MT</t>
+  </si>
+  <si>
+    <t>021/2025</t>
+  </si>
+  <si>
+    <t>001/2026</t>
+  </si>
+  <si>
+    <t>CE 011/2025</t>
+  </si>
+  <si>
+    <t>DL 005/2025</t>
   </si>
 </sst>
 </file>
@@ -1262,7 +1277,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:P51"/>
+  <dimension ref="A1:P53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" customWidth="1"/>
@@ -3549,6 +3564,73 @@
         <v>46007</v>
       </c>
     </row>
+    <row r="52" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>256</v>
+      </c>
+      <c r="C52" t="s">
+        <v>152</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="E52" s="1">
+        <v>46010</v>
+      </c>
+      <c r="H52" s="25">
+        <v>7304121.4800000004</v>
+      </c>
+      <c r="I52" t="s">
+        <v>259</v>
+      </c>
+      <c r="J52" t="s">
+        <v>19</v>
+      </c>
+      <c r="K52" t="s">
+        <v>20</v>
+      </c>
+      <c r="L52">
+        <v>1</v>
+      </c>
+      <c r="M52" s="1">
+        <v>46027</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
+        <v>257</v>
+      </c>
+      <c r="C53" t="s">
+        <v>152</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="E53" s="1">
+        <v>46055</v>
+      </c>
+      <c r="F53" s="1">
+        <v>46419</v>
+      </c>
+      <c r="H53" s="25">
+        <v>30599999.16</v>
+      </c>
+      <c r="I53" t="s">
+        <v>258</v>
+      </c>
+      <c r="J53" t="s">
+        <v>19</v>
+      </c>
+      <c r="K53" t="s">
+        <v>20</v>
+      </c>
+      <c r="L53">
+        <v>2</v>
+      </c>
+      <c r="M53" s="1">
+        <v>46078</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
@@ -3851,7 +3933,7 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1">
         <f ca="1">TODAY()</f>
-        <v>46084</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -3882,7 +3964,7 @@
       </c>
       <c r="D26" s="1">
         <f ca="1">TODAY()</f>
-        <v>46084</v>
+        <v>46093</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">

--- a/DADOS_CONTRATOS.xlsx
+++ b/DADOS_CONTRATOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48AA8F86-8B66-4058-AE07-1D682D863AD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0AAF82-F25C-40A7-B239-7E35F3B969A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="261">
   <si>
     <t>id</t>
   </si>
@@ -808,6 +808,9 @@
   </si>
   <si>
     <t>DL 005/2025</t>
+  </si>
+  <si>
+    <t>COOMSER - COOP. DE TRABALHO E SERVIÇOS DE RONDONÓPOLIS</t>
   </si>
 </sst>
 </file>
@@ -3569,7 +3572,7 @@
         <v>256</v>
       </c>
       <c r="C52" t="s">
-        <v>152</v>
+        <v>260</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>255</v>
@@ -3601,7 +3604,7 @@
         <v>257</v>
       </c>
       <c r="C53" t="s">
-        <v>152</v>
+        <v>260</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>255</v>

--- a/DADOS_CONTRATOS.xlsx
+++ b/DADOS_CONTRATOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0AAF82-F25C-40A7-B239-7E35F3B969A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13554757-0005-42C4-A3C2-D5E27320696A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -801,9 +801,6 @@
     <t>021/2025</t>
   </si>
   <si>
-    <t>001/2026</t>
-  </si>
-  <si>
     <t>CE 011/2025</t>
   </si>
   <si>
@@ -811,6 +808,9 @@
   </si>
   <si>
     <t>COOMSER - COOP. DE TRABALHO E SERVIÇOS DE RONDONÓPOLIS</t>
+  </si>
+  <si>
+    <t>004/2026</t>
   </si>
 </sst>
 </file>
@@ -1369,7 +1369,7 @@
         <v>45064</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G51" si="0">F2-E2</f>
+        <f t="shared" ref="G2:G52" si="0">F2-E2</f>
         <v>379</v>
       </c>
       <c r="H2" s="17">
@@ -3572,7 +3572,7 @@
         <v>256</v>
       </c>
       <c r="C52" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>255</v>
@@ -3580,11 +3580,18 @@
       <c r="E52" s="1">
         <v>46010</v>
       </c>
+      <c r="F52" s="1">
+        <v>46191</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="0"/>
+        <v>181</v>
+      </c>
       <c r="H52" s="25">
         <v>7304121.4800000004</v>
       </c>
       <c r="I52" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J52" t="s">
         <v>19</v>
@@ -3601,25 +3608,25 @@
     </row>
     <row r="53" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="C53" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>255</v>
       </c>
       <c r="E53" s="1">
-        <v>46055</v>
+        <v>46113</v>
       </c>
       <c r="F53" s="1">
-        <v>46419</v>
+        <v>46477</v>
       </c>
       <c r="H53" s="25">
         <v>30599999.16</v>
       </c>
       <c r="I53" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="J53" t="s">
         <v>19</v>
@@ -3628,10 +3635,10 @@
         <v>20</v>
       </c>
       <c r="L53">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M53" s="1">
-        <v>46078</v>
+        <v>46134</v>
       </c>
     </row>
   </sheetData>
@@ -3936,7 +3943,7 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1">
         <f ca="1">TODAY()</f>
-        <v>46093</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -3967,7 +3974,7 @@
       </c>
       <c r="D26" s="1">
         <f ca="1">TODAY()</f>
-        <v>46093</v>
+        <v>46154</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">

--- a/DADOS_CONTRATOS.xlsx
+++ b/DADOS_CONTRATOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13554757-0005-42C4-A3C2-D5E27320696A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{951FDD11-57AE-4C47-A981-A20512C76B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="262">
   <si>
     <t>id</t>
   </si>
@@ -807,10 +807,13 @@
     <t>DL 005/2025</t>
   </si>
   <si>
-    <t>COOMSER - COOP. DE TRABALHO E SERVIÇOS DE RONDONÓPOLIS</t>
-  </si>
-  <si>
     <t>004/2026</t>
+  </si>
+  <si>
+    <t>COOMSER COOP. DE TRABALHO E SERVIÇOS DE RONDONÓPOLIS</t>
+  </si>
+  <si>
+    <t>COOMSER  COOP. DE TRABALHO E SERVIÇOS DE RONDONÓPOLIS</t>
   </si>
 </sst>
 </file>
@@ -3572,7 +3575,7 @@
         <v>256</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>255</v>
@@ -3608,10 +3611,10 @@
     </row>
     <row r="53" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>255</v>

--- a/DADOS_CONTRATOS.xlsx
+++ b/DADOS_CONTRATOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{951FDD11-57AE-4C47-A981-A20512C76B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E90E77A2-BEC5-4DF8-B397-890695AD2BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="260">
   <si>
     <t>id</t>
   </si>
@@ -808,12 +808,6 @@
   </si>
   <si>
     <t>004/2026</t>
-  </si>
-  <si>
-    <t>COOMSER COOP. DE TRABALHO E SERVIÇOS DE RONDONÓPOLIS</t>
-  </si>
-  <si>
-    <t>COOMSER  COOP. DE TRABALHO E SERVIÇOS DE RONDONÓPOLIS</t>
   </si>
 </sst>
 </file>
@@ -3575,7 +3569,7 @@
         <v>256</v>
       </c>
       <c r="C52" t="s">
-        <v>260</v>
+        <v>222</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>255</v>
@@ -3614,7 +3608,7 @@
         <v>259</v>
       </c>
       <c r="C53" t="s">
-        <v>261</v>
+        <v>222</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>255</v>

--- a/DADOS_CONTRATOS.xlsx
+++ b/DADOS_CONTRATOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E90E77A2-BEC5-4DF8-B397-890695AD2BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E73083-25C2-4EB8-828F-E2889509CF37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="261">
   <si>
     <t>id</t>
   </si>
@@ -808,6 +808,9 @@
   </si>
   <si>
     <t>004/2026</t>
+  </si>
+  <si>
+    <t>COOMSER COOPERATIVA MISTA DE BENS E SERVICOS DE RONDONOPOLIS</t>
   </si>
 </sst>
 </file>
@@ -3569,7 +3572,7 @@
         <v>256</v>
       </c>
       <c r="C52" t="s">
-        <v>222</v>
+        <v>260</v>
       </c>
       <c r="D52" s="7" t="s">
         <v>255</v>
@@ -3608,7 +3611,7 @@
         <v>259</v>
       </c>
       <c r="C53" t="s">
-        <v>222</v>
+        <v>260</v>
       </c>
       <c r="D53" s="7" t="s">
         <v>255</v>

--- a/DADOS_CONTRATOS.xlsx
+++ b/DADOS_CONTRATOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9E73083-25C2-4EB8-828F-E2889509CF37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12B7408-B328-4B49-B009-D74C3441DF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="265">
   <si>
     <t>id</t>
   </si>
@@ -811,6 +811,18 @@
   </si>
   <si>
     <t>COOMSER COOPERATIVA MISTA DE BENS E SERVICOS DE RONDONOPOLIS</t>
+  </si>
+  <si>
+    <t>016/2025</t>
+  </si>
+  <si>
+    <t>BIO GS CONSULTORIA AMBIENTAL LTDA</t>
+  </si>
+  <si>
+    <t>REGULARIZAÇÃO DO USO DE RECURSOS HÍDRICOS SUBTERRÂNEOS MEDIANTE OBTENÇÃO DE OUTORGA JUNTO AO ÓRGÃO AMBIENTAL COMPETENTE E EXECUÇÃO DO TAMPONAMENTO DEFINITIVO DE POÇOS TUBULARES PROFUNDOS DESATIVADOS</t>
+  </si>
+  <si>
+    <t>CE 009/2025</t>
   </si>
 </sst>
 </file>
@@ -919,7 +931,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -965,6 +977,7 @@
     </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1280,7 +1293,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:P53"/>
+  <dimension ref="A1:P54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" customWidth="1"/>
@@ -1369,7 +1382,7 @@
         <v>45064</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G52" si="0">F2-E2</f>
+        <f t="shared" ref="G2:G54" si="0">F2-E2</f>
         <v>379</v>
       </c>
       <c r="H2" s="17">
@@ -3622,6 +3635,10 @@
       <c r="F53" s="1">
         <v>46477</v>
       </c>
+      <c r="G53">
+        <f t="shared" si="0"/>
+        <v>364</v>
+      </c>
       <c r="H53" s="25">
         <v>30599999.16</v>
       </c>
@@ -3639,6 +3656,45 @@
       </c>
       <c r="M53" s="1">
         <v>46134</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
+        <v>261</v>
+      </c>
+      <c r="C54" t="s">
+        <v>262</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="E54" s="1">
+        <v>45985</v>
+      </c>
+      <c r="F54" s="1">
+        <v>46530</v>
+      </c>
+      <c r="G54">
+        <f t="shared" si="0"/>
+        <v>545</v>
+      </c>
+      <c r="H54" s="29">
+        <v>703999.99</v>
+      </c>
+      <c r="I54" t="s">
+        <v>264</v>
+      </c>
+      <c r="J54" t="s">
+        <v>19</v>
+      </c>
+      <c r="K54" t="s">
+        <v>163</v>
+      </c>
+      <c r="L54">
+        <v>45</v>
+      </c>
+      <c r="M54" s="1">
+        <v>45987</v>
       </c>
     </row>
   </sheetData>
@@ -3943,7 +3999,7 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1">
         <f ca="1">TODAY()</f>
-        <v>46154</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -3974,7 +4030,7 @@
       </c>
       <c r="D26" s="1">
         <f ca="1">TODAY()</f>
-        <v>46154</v>
+        <v>46170</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">

--- a/DADOS_CONTRATOS.xlsx
+++ b/DADOS_CONTRATOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C12B7408-B328-4B49-B009-D74C3441DF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF8E60A-2C68-49F5-A7DA-F6B8772B2BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="618" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="282">
   <si>
     <t>id</t>
   </si>
@@ -823,13 +823,64 @@
   </si>
   <si>
     <t>CE 009/2025</t>
+  </si>
+  <si>
+    <t>005/2026</t>
+  </si>
+  <si>
+    <t>SM7 ENGENHARIA, TECNOLOGIA E IMPORTAÇÃO LTDA.</t>
+  </si>
+  <si>
+    <t>ELABORAÇÃO DE PROJETO EXECUTIVO, FORNECIMENTO E IMPLANTAÇÃO DE UM RESERVATÓRIO METÁLICO APOIADO, PARAFUSADO, COM REVESTIMENTO VITRIFICADO E COBERTURA DO TIPO DOMOS GEODÉSICO EM ALUMÍNIO, COM CAPACIDADE VOLUMÉTRICA NOMINAL DE 2.500 M³</t>
+  </si>
+  <si>
+    <t>CE 001/2026</t>
+  </si>
+  <si>
+    <t>NOVOPAC</t>
+  </si>
+  <si>
+    <t>008/2026</t>
+  </si>
+  <si>
+    <t>TN CONSTRUÇÕES E SERVIÇOS LTDA.</t>
+  </si>
+  <si>
+    <t>EXECUÇÃO DE REDES DE ESGOTAMENTO SANITÁRIO NO LOTEAMENTO RODOVIÁRIO, NO MUNICÍPIO DE RONDONÓPOLIS – MT, COMPREENDENDO MÃO DE OBRA, EQUIPAMENTOS, EXECUÇÃO DE LIGAÇÕES DOMICILIARES, POÇOS DE VISITA, RECOMPOSIÇÃO DE PAVIMENTOS E TESTES OPERACIONAIS, , COM RECURSO FEDERAL DO NOVO PAC - TERMO DE COMPROMISSO Nº 968724/2024 - OPERAÇÃO 1098319-94 - OGU</t>
+  </si>
+  <si>
+    <t>CE 003/2026</t>
+  </si>
+  <si>
+    <t>NEXXERA TECNOLOGIA E SERVIÇOS S.A.</t>
+  </si>
+  <si>
+    <t>009/2026</t>
+  </si>
+  <si>
+    <t>010/2026</t>
+  </si>
+  <si>
+    <t>PRESTAÇÃO DE SERVIÇOS DE REDE DE VALOR AGREGADO (VALUE ADDED NETWORK – VAN BANCÁRIA) DESTINADA AO INTERCÂMBIO DE DADOS FINANCEIROS E AO RECONHECIMENTO AUTOMÁTICO E INSTANTÂNEO DOS PAGAMENTOS BANCÁRIOS RECEBIDOS POR ESTA AUTARQUIA</t>
+  </si>
+  <si>
+    <t>WM ESTUDOS E CONSULTORIA EIRELI</t>
+  </si>
+  <si>
+    <t>SERVIÇOS ESPECIALIZADOS DE ENGENHARIA CONSULTIVA PARA ELABORAÇÃO DE ESTUDOS TÉCNICOS, DIMENSIONAMENTOS   E PROJETOS EXECUTIVOS VOLTADOS À REESTRUTURAÇÃO DA CÂMARA DE SUCÇÃO  E BARRILETES DA ESTAÇÃO ELEVATÓRIA DE ÁGUA BRUTA 2 (EEAB2) INCLUINDO O SISTEMA DE DESCARGA DO DESARENADOR E A ADEQUAÇÃO/IMPLANTAÇÃO DAS BACIAS DE CONTENÇÃO PARA ACONDICIONAMENTO DE TANQUES DE PRODUTOS QUÍMICOS (PAC E SODA CÁUSTICA) PARA AS ESTAÇÕES DE TRATAMENTO DE ÁGUA (ETAS) 1 E 2</t>
+  </si>
+  <si>
+    <t>DL 003/2026</t>
+  </si>
+  <si>
+    <t>DL 002/2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -867,6 +918,13 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -931,7 +989,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -978,6 +1036,7 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1293,12 +1352,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:P54"/>
+  <dimension ref="A1:P58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="41.5703125" customWidth="1"/>
+    <col min="3" max="3" width="61.7109375" customWidth="1"/>
     <col min="4" max="4" width="36" customWidth="1"/>
     <col min="5" max="5" width="12" customWidth="1"/>
     <col min="6" max="6" width="11.5703125" customWidth="1"/>
@@ -1382,7 +1441,7 @@
         <v>45064</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G54" si="0">F2-E2</f>
+        <f t="shared" ref="G2:G58" si="0">F2-E2</f>
         <v>379</v>
       </c>
       <c r="H2" s="17">
@@ -3695,6 +3754,162 @@
       </c>
       <c r="M54" s="1">
         <v>45987</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
+        <v>265</v>
+      </c>
+      <c r="C55" t="s">
+        <v>266</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="E55" s="1">
+        <v>46146</v>
+      </c>
+      <c r="F55" s="1">
+        <v>46510</v>
+      </c>
+      <c r="G55">
+        <f t="shared" si="0"/>
+        <v>364</v>
+      </c>
+      <c r="H55" s="30">
+        <v>3248774.8</v>
+      </c>
+      <c r="I55" t="s">
+        <v>268</v>
+      </c>
+      <c r="J55" t="s">
+        <v>269</v>
+      </c>
+      <c r="K55" t="s">
+        <v>20</v>
+      </c>
+      <c r="L55">
+        <v>6</v>
+      </c>
+      <c r="M55" s="1">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+      <c r="B56" t="s">
+        <v>270</v>
+      </c>
+      <c r="C56" t="s">
+        <v>271</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="E56" s="1">
+        <v>46162</v>
+      </c>
+      <c r="F56" s="1">
+        <v>46526</v>
+      </c>
+      <c r="G56">
+        <f t="shared" si="0"/>
+        <v>364</v>
+      </c>
+      <c r="H56" s="30">
+        <v>700756.21</v>
+      </c>
+      <c r="I56" t="s">
+        <v>273</v>
+      </c>
+      <c r="J56" t="s">
+        <v>269</v>
+      </c>
+      <c r="K56" t="s">
+        <v>20</v>
+      </c>
+      <c r="L56">
+        <v>9</v>
+      </c>
+      <c r="M56" s="1">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+      <c r="B57" t="s">
+        <v>275</v>
+      </c>
+      <c r="C57" t="s">
+        <v>274</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="E57" s="1">
+        <v>46162</v>
+      </c>
+      <c r="F57" s="1">
+        <v>46526</v>
+      </c>
+      <c r="G57">
+        <f t="shared" si="0"/>
+        <v>364</v>
+      </c>
+      <c r="H57" s="30">
+        <v>51148.24</v>
+      </c>
+      <c r="I57" t="s">
+        <v>281</v>
+      </c>
+      <c r="J57" t="s">
+        <v>19</v>
+      </c>
+      <c r="K57" t="s">
+        <v>20</v>
+      </c>
+      <c r="L57">
+        <v>10</v>
+      </c>
+      <c r="M57" s="1">
+        <v>46167</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="240" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>276</v>
+      </c>
+      <c r="C58" t="s">
+        <v>278</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="E58" s="1">
+        <v>46162</v>
+      </c>
+      <c r="F58" s="1">
+        <v>46222</v>
+      </c>
+      <c r="G58">
+        <f t="shared" si="0"/>
+        <v>60</v>
+      </c>
+      <c r="H58" s="30">
+        <v>59200</v>
+      </c>
+      <c r="I58" t="s">
+        <v>280</v>
+      </c>
+      <c r="J58" t="s">
+        <v>19</v>
+      </c>
+      <c r="K58" t="s">
+        <v>20</v>
+      </c>
+      <c r="L58">
+        <v>11</v>
+      </c>
+      <c r="M58" s="1">
+        <v>46167</v>
       </c>
     </row>
   </sheetData>
@@ -3999,7 +4214,7 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1">
         <f ca="1">TODAY()</f>
-        <v>46170</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -4030,7 +4245,7 @@
       </c>
       <c r="D26" s="1">
         <f ca="1">TODAY()</f>
-        <v>46170</v>
+        <v>46171</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">

--- a/DADOS_CONTRATOS.xlsx
+++ b/DADOS_CONTRATOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AF8E60A-2C68-49F5-A7DA-F6B8772B2BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7C6493-73D7-4878-8EA5-C1E617548D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="287">
   <si>
     <t>id</t>
   </si>
@@ -874,6 +874,21 @@
   </si>
   <si>
     <t>DL 002/2026</t>
+  </si>
+  <si>
+    <t>003/2026</t>
+  </si>
+  <si>
+    <t>SOCIEDADE IMPRESSORA SOUZA LTDA</t>
+  </si>
+  <si>
+    <t>PRESTAÇÃO DE SERVIÇOS DE PUBLICIDADE LEGAL, CONSISTENTES NA PUBLICAÇÃO DE AVISOS DE LICITAÇÃO E DEMAIS MATÉRIAS DE INTERESSE DO SANEAR, EM JORNAL DIÁRIO IMPRESSO DE GRANDE CIRCULAÇÃO NO MUNICÍPIO DE RONDONÓPOLIS/MT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISABELLA GUIMARAES SOUZA </t>
+  </si>
+  <si>
+    <t>IN 002/2026</t>
   </si>
 </sst>
 </file>
@@ -1352,7 +1367,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:P58"/>
+  <dimension ref="A1:P59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.28515625" customWidth="1"/>
@@ -1441,7 +1456,7 @@
         <v>45064</v>
       </c>
       <c r="G2" s="4">
-        <f t="shared" ref="G2:G58" si="0">F2-E2</f>
+        <f t="shared" ref="G2:G59" si="0">F2-E2</f>
         <v>379</v>
       </c>
       <c r="H2" s="17">
@@ -3910,6 +3925,45 @@
       </c>
       <c r="M58" s="1">
         <v>46167</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>282</v>
+      </c>
+      <c r="C59" t="s">
+        <v>283</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="E59" s="1">
+        <v>46098</v>
+      </c>
+      <c r="F59" s="1">
+        <v>46462</v>
+      </c>
+      <c r="G59">
+        <f t="shared" si="0"/>
+        <v>364</v>
+      </c>
+      <c r="H59" s="30">
+        <v>30000</v>
+      </c>
+      <c r="I59" t="s">
+        <v>286</v>
+      </c>
+      <c r="J59" t="s">
+        <v>19</v>
+      </c>
+      <c r="K59" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="L59">
+        <v>4</v>
+      </c>
+      <c r="M59" s="1">
+        <v>46104</v>
       </c>
     </row>
   </sheetData>
@@ -4214,7 +4268,7 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46176</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -4245,7 +4299,7 @@
       </c>
       <c r="D26" s="1">
         <f ca="1">TODAY()</f>
-        <v>46171</v>
+        <v>46176</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">

--- a/DADOS_CONTRATOS.xlsx
+++ b/DADOS_CONTRATOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD7C6493-73D7-4878-8EA5-C1E617548D0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE02853B-611B-4232-8B82-C666AE0F0676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -852,18 +852,12 @@
     <t>CE 003/2026</t>
   </si>
   <si>
-    <t>NEXXERA TECNOLOGIA E SERVIÇOS S.A.</t>
-  </si>
-  <si>
     <t>009/2026</t>
   </si>
   <si>
     <t>010/2026</t>
   </si>
   <si>
-    <t>PRESTAÇÃO DE SERVIÇOS DE REDE DE VALOR AGREGADO (VALUE ADDED NETWORK – VAN BANCÁRIA) DESTINADA AO INTERCÂMBIO DE DADOS FINANCEIROS E AO RECONHECIMENTO AUTOMÁTICO E INSTANTÂNEO DOS PAGAMENTOS BANCÁRIOS RECEBIDOS POR ESTA AUTARQUIA</t>
-  </si>
-  <si>
     <t>WM ESTUDOS E CONSULTORIA EIRELI</t>
   </si>
   <si>
@@ -889,6 +883,12 @@
   </si>
   <si>
     <t>IN 002/2026</t>
+  </si>
+  <si>
+    <t>PRESTAÇÃO DE SERVIÇOS DE REDE DE VALOR AGREGADO (VALUE ADDED NETWORK  VAN BANCÁRIA) DESTINADA AO INTERCÂMBIO DE DADOS FINANCEIROS E AO RECONHECIMENTO AUTOMÁTICO E INSTANTÂNEO DOS PAGAMENTOS BANCÁRIOS RECEBIDOS POR ESTA AUTARQUIA</t>
+  </si>
+  <si>
+    <t>NEXXERA TECNOLOGIA E SERVICOS S.A.</t>
   </si>
 </sst>
 </file>
@@ -3851,13 +3851,13 @@
     </row>
     <row r="57" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C57" t="s">
-        <v>274</v>
+        <v>286</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="E57" s="1">
         <v>46162</v>
@@ -3873,7 +3873,7 @@
         <v>51148.24</v>
       </c>
       <c r="I57" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="J57" t="s">
         <v>19</v>
@@ -3890,13 +3890,13 @@
     </row>
     <row r="58" spans="1:13" ht="240" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
+        <v>275</v>
+      </c>
+      <c r="C58" t="s">
         <v>276</v>
       </c>
-      <c r="C58" t="s">
-        <v>278</v>
-      </c>
       <c r="D58" s="7" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E58" s="1">
         <v>46162</v>
@@ -3912,7 +3912,7 @@
         <v>59200</v>
       </c>
       <c r="I58" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="J58" t="s">
         <v>19</v>
@@ -3929,13 +3929,13 @@
     </row>
     <row r="59" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
+        <v>280</v>
+      </c>
+      <c r="C59" t="s">
+        <v>281</v>
+      </c>
+      <c r="D59" s="7" t="s">
         <v>282</v>
-      </c>
-      <c r="C59" t="s">
-        <v>283</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>284</v>
       </c>
       <c r="E59" s="1">
         <v>46098</v>
@@ -3951,13 +3951,13 @@
         <v>30000</v>
       </c>
       <c r="I59" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="J59" t="s">
         <v>19</v>
       </c>
       <c r="K59" s="28" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="L59">
         <v>4</v>
@@ -4268,7 +4268,7 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1">
         <f ca="1">TODAY()</f>
-        <v>46176</v>
+        <v>46190</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="D26" s="1">
         <f ca="1">TODAY()</f>
-        <v>46176</v>
+        <v>46190</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">

--- a/DADOS_CONTRATOS.xlsx
+++ b/DADOS_CONTRATOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE02853B-611B-4232-8B82-C666AE0F0676}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAFA6042-8F16-4050-8C2E-5DB93094E782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -846,9 +846,6 @@
     <t>TN CONSTRUÇÕES E SERVIÇOS LTDA.</t>
   </si>
   <si>
-    <t>EXECUÇÃO DE REDES DE ESGOTAMENTO SANITÁRIO NO LOTEAMENTO RODOVIÁRIO, NO MUNICÍPIO DE RONDONÓPOLIS – MT, COMPREENDENDO MÃO DE OBRA, EQUIPAMENTOS, EXECUÇÃO DE LIGAÇÕES DOMICILIARES, POÇOS DE VISITA, RECOMPOSIÇÃO DE PAVIMENTOS E TESTES OPERACIONAIS, , COM RECURSO FEDERAL DO NOVO PAC - TERMO DE COMPROMISSO Nº 968724/2024 - OPERAÇÃO 1098319-94 - OGU</t>
-  </si>
-  <si>
     <t>CE 003/2026</t>
   </si>
   <si>
@@ -889,6 +886,9 @@
   </si>
   <si>
     <t>NEXXERA TECNOLOGIA E SERVICOS S.A.</t>
+  </si>
+  <si>
+    <t>EXECUÇÃO DE REDES DE ESGOTAMENTO SANITÁRIO NO LOTEAMENTO RODOVIÁRIO, NO MUNICÍPIO DE RONDONÓPOLIS MT, COMPREENDENDO MÃO DE OBRA, EQUIPAMENTOS, EXECUÇÃO DE LIGAÇÕES DOMICILIARES, POÇOS DE VISITA, RECOMPOSIÇÃO DE PAVIMENTOS E TESTES OPERACIONAIS, , COM RECURSO FEDERAL DO NOVO PAC - TERMO DE COMPROMISSO Nº 968724/2024  OPERAÇÃO 1098319-94 - OGU</t>
   </si>
 </sst>
 </file>
@@ -3818,7 +3818,7 @@
         <v>271</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="E56" s="1">
         <v>46162</v>
@@ -3834,7 +3834,7 @@
         <v>700756.21</v>
       </c>
       <c r="I56" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="J56" t="s">
         <v>269</v>
@@ -3851,13 +3851,13 @@
     </row>
     <row r="57" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C57" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E57" s="1">
         <v>46162</v>
@@ -3873,7 +3873,7 @@
         <v>51148.24</v>
       </c>
       <c r="I57" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="J57" t="s">
         <v>19</v>
@@ -3890,13 +3890,13 @@
     </row>
     <row r="58" spans="1:13" ht="240" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
+        <v>274</v>
+      </c>
+      <c r="C58" t="s">
         <v>275</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" s="7" t="s">
         <v>276</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>277</v>
       </c>
       <c r="E58" s="1">
         <v>46162</v>
@@ -3912,7 +3912,7 @@
         <v>59200</v>
       </c>
       <c r="I58" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="J58" t="s">
         <v>19</v>
@@ -3929,13 +3929,13 @@
     </row>
     <row r="59" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
+        <v>279</v>
+      </c>
+      <c r="C59" t="s">
         <v>280</v>
       </c>
-      <c r="C59" t="s">
+      <c r="D59" s="7" t="s">
         <v>281</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>282</v>
       </c>
       <c r="E59" s="1">
         <v>46098</v>
@@ -3951,13 +3951,13 @@
         <v>30000</v>
       </c>
       <c r="I59" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J59" t="s">
         <v>19</v>
       </c>
       <c r="K59" s="28" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="L59">
         <v>4</v>
@@ -4268,7 +4268,7 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46191</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="D26" s="1">
         <f ca="1">TODAY()</f>
-        <v>46190</v>
+        <v>46191</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">

--- a/DADOS_CONTRATOS.xlsx
+++ b/DADOS_CONTRATOS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAFA6042-8F16-4050-8C2E-5DB93094E782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21630DDC-C196-4548-A7F7-255BA1057B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="288">
   <si>
     <t>id</t>
   </si>
@@ -889,6 +889,9 @@
   </si>
   <si>
     <t>EXECUÇÃO DE REDES DE ESGOTAMENTO SANITÁRIO NO LOTEAMENTO RODOVIÁRIO, NO MUNICÍPIO DE RONDONÓPOLIS MT, COMPREENDENDO MÃO DE OBRA, EQUIPAMENTOS, EXECUÇÃO DE LIGAÇÕES DOMICILIARES, POÇOS DE VISITA, RECOMPOSIÇÃO DE PAVIMENTOS E TESTES OPERACIONAIS, , COM RECURSO FEDERAL DO NOVO PAC - TERMO DE COMPROMISSO Nº 968724/2024  OPERAÇÃO 1098319-94 - OGU</t>
+  </si>
+  <si>
+    <t>OPERAÇÃO, MANUTENÇÃO E CONSERVAÇÃO DO SISTEMA PÚBLICO DE ABASTECIMENTO DE ÁGUA DO MUNICÍPIO DE RONDONÓPOLIS - MT</t>
   </si>
 </sst>
 </file>
@@ -3701,7 +3704,7 @@
         <v>260</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>255</v>
+        <v>287</v>
       </c>
       <c r="E53" s="1">
         <v>46113</v>
@@ -4268,7 +4271,7 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1">
         <f ca="1">TODAY()</f>
-        <v>46191</v>
+        <v>46212</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -4299,7 +4302,7 @@
       </c>
       <c r="D26" s="1">
         <f ca="1">TODAY()</f>
-        <v>46191</v>
+        <v>46212</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
